--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/ALABAMA_2023.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/ALABAMA_2023.xlsx
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C109">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C130">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C210">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C216">
